--- a/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
-    <t>ID</t>
+    <t>Id</t>
   </si>
   <si>
     <t>Key</t>
@@ -411,13 +411,13 @@
     <font>
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11.5"/>
       <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5D198A-9C50-427E-B010-3643D16E909A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE917980-073F-4F1A-A781-E4AD0DA8F5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyConfig" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -97,9 +97,6 @@
       </rPr>
       <t>点伤害。</t>
     </r>
-  </si>
-  <si>
-    <t>brute</t>
   </si>
   <si>
     <t>大块头</t>
@@ -255,6 +252,28 @@
   </si>
   <si>
     <t>蓄力倍率</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI类型</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>brute</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime</t>
+  </si>
+  <si>
+    <t>Brute</t>
+  </si>
+  <si>
+    <t>Default</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -840,14 +859,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
-    <col min="8" max="9" width="19.88671875" customWidth="1"/>
+    <col min="8" max="10" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -861,22 +880,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -890,13 +912,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
         <v>6</v>
@@ -904,8 +926,11 @@
       <c r="I2" t="s">
         <v>7</v>
       </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -919,22 +944,25 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -960,18 +988,21 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
       </c>
       <c r="D5">
         <v>45</v>
@@ -989,18 +1020,21 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -1018,18 +1052,21 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>40</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -1047,18 +1084,21 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
       </c>
       <c r="D8">
         <v>50</v>
@@ -1076,18 +1116,21 @@
         <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>40</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -1105,7 +1148,10 @@
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE917980-073F-4F1A-A781-E4AD0DA8F5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE311EDB-7433-48FA-A9D2-F061B341581F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,288 +31,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
   <si>
-    <t>Key</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
     <t>MaxHp</t>
   </si>
   <si>
-    <t>BaseBlock</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>资源key</t>
-  </si>
-  <si>
     <t>名称</t>
   </si>
   <si>
     <t>血量</t>
   </si>
   <si>
-    <t>护甲</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>slime</t>
-  </si>
-  <si>
-    <t>史莱姆</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>造成{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
-  </si>
-  <si>
-    <t>大块头</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
-  </si>
-  <si>
-    <t>assassin</t>
-  </si>
-  <si>
-    <t>暗影刺客</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>获得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点格挡。</t>
-    </r>
-  </si>
-  <si>
-    <t>archer</t>
-  </si>
-  <si>
-    <t>哥布林弓手</t>
-  </si>
-  <si>
-    <t>knight</t>
-  </si>
-  <si>
-    <t>精英骑士</t>
-  </si>
-  <si>
-    <t>lich</t>
-  </si>
-  <si>
-    <t>巫妖</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{0}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11.5"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>Defend</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>StrongRate</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓄力倍率</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>AIType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AI类型</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>brute</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime</t>
-  </si>
-  <si>
-    <t>Brute</t>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>稀有度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩小甲虫</t>
+  </si>
+  <si>
+    <t>shrinker_beetle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Actions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树枝史莱姆</t>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,1,2]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>twig_slime_s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.25"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11.5"/>
-      <color rgb="FF0F1115"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -330,23 +138,18 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -363,20 +166,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -859,303 +653,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
-    <col min="8" max="10" width="19.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" t="s">
-        <v>5</v>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
+      <c r="B4" t="s">
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>40</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>15</v>
+      <c r="G4" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>37</v>
+      <c r="B5" t="s">
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="G5" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>8</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>60</v>
-      </c>
-      <c r="E9">
-        <v>9</v>
-      </c>
-      <c r="F9">
-        <v>6</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE311EDB-7433-48FA-A9D2-F061B341581F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2415ED-ED57-4C87-B7A6-1CCBD236F2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyConfig" sheetId="1" r:id="rId1"/>
@@ -749,7 +749,7 @@
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2415ED-ED57-4C87-B7A6-1CCBD236F2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920A02BB-D974-4AD2-8536-3B22E0B432D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="1776" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyConfig" sheetId="1" r:id="rId1"/>
@@ -31,71 +31,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+  <si>
+    <t>Twig_slime_s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Twig_slime_m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树枝史莱姆(小)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树枝史莱姆（中）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MaxHp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Actions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>血量</t>
-  </si>
-  <si>
-    <t>AIType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>稀有度</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shrinker_beetle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>缩小甲虫</t>
-  </si>
-  <si>
-    <t>shrinker_beetle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Actions</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>树枝史莱姆</t>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0,1,2]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -103,18 +113,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[0,1,2]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>twig_slime_s</t>
+    <t>Byrdonis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多尼斯异鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>墨影幻灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vantom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4,5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6,7]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[8,9,10,11]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,13 +166,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -653,128 +681,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
     <col min="6" max="6" width="12.88671875" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>40</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>80</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>180</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
